--- a/outputs/df_summary.xlsx
+++ b/outputs/df_summary.xlsx
@@ -481,10 +481,10 @@
         <v>64.70588235294117</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1521810521594259</v>
+        <v>14.73826893502499</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01637170019522961</v>
+        <v>0.540266106442577</v>
       </c>
       <c r="G2" t="n">
         <v>14.59515570934256</v>
@@ -493,7 +493,7 @@
         <v>2.826989619377162</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9363192751792114</v>
+        <v>0.513528110788035</v>
       </c>
     </row>
     <row r="3">
@@ -514,10 +514,10 @@
         <v>64.70588235294117</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09819009101723046</v>
+        <v>0.1064666745304477</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01863116626115391</v>
+        <v>0.01863119759429716</v>
       </c>
       <c r="G3" t="n">
         <v>14.59515570934256</v>
@@ -526,7 +526,7 @@
         <v>2.826989619377162</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8068726999745424</v>
+        <v>0.84485263524258</v>
       </c>
     </row>
     <row r="4">
@@ -547,10 +547,10 @@
         <v>64.70588235294117</v>
       </c>
       <c r="E4" t="n">
-        <v>194.9809087850827</v>
+        <v>0.08808064577119654</v>
       </c>
       <c r="F4" t="n">
-        <v>2.695063025210084</v>
+        <v>0.01680088481836223</v>
       </c>
       <c r="G4" t="n">
         <v>14.59515570934256</v>
@@ -559,7 +559,7 @@
         <v>2.826989619377162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3131864425484232</v>
+        <v>0.8716715119175223</v>
       </c>
     </row>
     <row r="5">
@@ -580,10 +580,10 @@
         <v>64.70588235294117</v>
       </c>
       <c r="E5" t="n">
-        <v>2.933680553834503</v>
+        <v>2.933680553834559</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5462430571101922</v>
+        <v>0.546243057110198</v>
       </c>
       <c r="G5" t="n">
         <v>14.59515570934256</v>
@@ -592,7 +592,7 @@
         <v>2.826989619377162</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5572108712743685</v>
+        <v>0.5572108712743635</v>
       </c>
     </row>
     <row r="6">
@@ -613,10 +613,10 @@
         <v>64.70588235294117</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1581029555213174</v>
+        <v>0.1581029555213172</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005540200941330786</v>
+        <v>0.005540200941330832</v>
       </c>
       <c r="G6" t="n">
         <v>14.59515570934256</v>
@@ -625,7 +625,7 @@
         <v>2.826989619377162</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9405323209960483</v>
+        <v>0.9405323209960484</v>
       </c>
     </row>
     <row r="7">
@@ -643,13 +643,13 @@
         <v>85.29411764705883</v>
       </c>
       <c r="D7" t="n">
-        <v>35.29411764705883</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="E7" t="n">
         <v>0.1049835424727344</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01554664679795562</v>
+        <v>0.01554664679795562</v>
       </c>
       <c r="G7" t="n">
         <v>14.59515570934256</v>
@@ -664,7 +664,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -679,10 +679,10 @@
         <v>64.28571428571429</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06269841269841268</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05340136054421769</v>
+        <v>0.7476190476190475</v>
       </c>
       <c r="G8" t="n">
         <v>1.822222222222222</v>
@@ -691,13 +691,13 @@
         <v>1.848888888888889</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9034406316833</v>
+        <v>0.7178735855004676</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -712,10 +712,10 @@
         <v>71.42857142857143</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05493773133155629</v>
+        <v>0.05493702910802002</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05307561095378826</v>
+        <v>0.05307564812653366</v>
       </c>
       <c r="G9" t="n">
         <v>1.822222222222222</v>
@@ -724,13 +724,13 @@
         <v>1.848888888888889</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8326444083768879</v>
+        <v>0.8326414692935658</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -745,10 +745,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="E10" t="n">
-        <v>1.588888888888889</v>
+        <v>0.0425256361349017</v>
       </c>
       <c r="F10" t="n">
-        <v>1.558333333333332</v>
+        <v>0.04407632269396146</v>
       </c>
       <c r="G10" t="n">
         <v>1.822222222222222</v>
@@ -757,13 +757,13 @@
         <v>1.848888888888889</v>
       </c>
       <c r="I10" t="n">
-        <v>0.425032364029106</v>
+        <v>0.8850061182973945</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -778,10 +778,10 @@
         <v>71.42857142857143</v>
       </c>
       <c r="E11" t="n">
-        <v>1.14326616106595</v>
+        <v>1.143266161065944</v>
       </c>
       <c r="F11" t="n">
-        <v>1.056830987739686</v>
+        <v>1.056830987739664</v>
       </c>
       <c r="G11" t="n">
         <v>1.822222222222222</v>
@@ -790,13 +790,13 @@
         <v>1.848888888888889</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5490533827268058</v>
+        <v>0.5490533827268069</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -811,10 +811,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008858556020230795</v>
+        <v>0.008858556020230749</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007555201614078522</v>
+        <v>0.00755520161407849</v>
       </c>
       <c r="G12" t="n">
         <v>1.822222222222222</v>
@@ -823,13 +823,13 @@
         <v>1.848888888888889</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8901511472818499</v>
+        <v>0.8901511472818533</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -844,10 +844,10 @@
         <v>71.42857142857143</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03181544235224387</v>
+        <v>0.03181544235224385</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03193751752025641</v>
+        <v>0.03193751752025635</v>
       </c>
       <c r="G13" t="n">
         <v>1.822222222222222</v>
@@ -856,7 +856,7 @@
         <v>1.848888888888889</v>
       </c>
       <c r="I13" t="n">
-        <v>0.808651747534306</v>
+        <v>0.8086517475343058</v>
       </c>
     </row>
     <row r="14">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>87.01298701298701</v>
+        <v>84.41558441558442</v>
       </c>
       <c r="D14" t="n">
         <v>63.63636363636363</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09284814741086868</v>
+        <v>29.75583369867728</v>
       </c>
       <c r="F14" t="n">
-        <v>0.009484901158687898</v>
+        <v>0.7208524880602801</v>
       </c>
       <c r="G14" t="n">
         <v>36.006746500253</v>
@@ -889,7 +889,7 @@
         <v>4.372744138977906</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8101234193795308</v>
+        <v>0.5661061036148849</v>
       </c>
     </row>
     <row r="15">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>88.31168831168831</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="D15" t="n">
         <v>71.42857142857143</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05588736877938218</v>
+        <v>0.08714169107241633</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01125493460616101</v>
+        <v>0.01125498474431228</v>
       </c>
       <c r="G15" t="n">
         <v>36.006746500253</v>
@@ -922,7 +922,7 @@
         <v>4.372744138977906</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6029830542847382</v>
+        <v>0.7331854728671104</v>
       </c>
     </row>
     <row r="16">
@@ -943,10 +943,10 @@
         <v>63.63636363636363</v>
       </c>
       <c r="E16" t="n">
-        <v>1564.707241307984</v>
+        <v>0.08169837564451538</v>
       </c>
       <c r="F16" t="n">
-        <v>4.139746472863355</v>
+        <v>0.009815725218786618</v>
       </c>
       <c r="G16" t="n">
         <v>36.006746500253</v>
@@ -954,7 +954,9 @@
       <c r="H16" t="n">
         <v>4.372744138977906</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.7731211131118579</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -974,10 +976,10 @@
         <v>67.53246753246754</v>
       </c>
       <c r="E17" t="n">
-        <v>2.265731533777893</v>
+        <v>2.265731533777923</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5159008079900016</v>
+        <v>0.5159008079900007</v>
       </c>
       <c r="G17" t="n">
         <v>36.006746500253</v>
@@ -986,7 +988,7 @@
         <v>4.372744138977906</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4975587060571409</v>
+        <v>0.4975587060571401</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1009,10 @@
         <v>62.33766233766234</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3977202311721809</v>
+        <v>0.3977202311721808</v>
       </c>
       <c r="F18" t="n">
-        <v>0.007421406718586268</v>
+        <v>0.007421406718586291</v>
       </c>
       <c r="G18" t="n">
         <v>36.006746500253</v>
@@ -1019,7 +1021,7 @@
         <v>4.372744138977906</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8467021754310698</v>
+        <v>0.8467021754310701</v>
       </c>
     </row>
     <row r="19">
@@ -1037,13 +1039,13 @@
         <v>85.71428571428571</v>
       </c>
       <c r="D19" t="n">
-        <v>28.57142857142857</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08679324007067814</v>
+        <v>0.08679324007067817</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.009773079793704949</v>
+        <v>0.009773079793704948</v>
       </c>
       <c r="G19" t="n">
         <v>36.006746500253</v>
@@ -1067,16 +1069,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>84.78581979320532</v>
+        <v>84.97045790251107</v>
       </c>
       <c r="D20" t="n">
-        <v>67.39871260886028</v>
+        <v>68.6482393032942</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00285694043665733</v>
+        <v>7.733737762031392</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0003339507731790378</v>
+        <v>0.9040047429956555</v>
       </c>
       <c r="G20" t="n">
         <v>27.33008493898488</v>
@@ -1085,7 +1087,7 @@
         <v>3.838074287247806</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3545660717845175</v>
+        <v>0.6033218365128165</v>
       </c>
     </row>
     <row r="21">
@@ -1100,16 +1102,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>96.82422451994091</v>
+        <v>93.9069423929099</v>
       </c>
       <c r="D21" t="n">
-        <v>80.15903067020068</v>
+        <v>79.9697084437713</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01256470689122768</v>
+        <v>0.0125595008330026</v>
       </c>
       <c r="F21" t="n">
-        <v>0.003510126054151395</v>
+        <v>0.003509869408000002</v>
       </c>
       <c r="G21" t="n">
         <v>27.33008493898488</v>
@@ -1118,7 +1120,7 @@
         <v>3.838074287247806</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2627029615954707</v>
+        <v>-0.2627738571625132</v>
       </c>
     </row>
     <row r="22">
@@ -1133,16 +1135,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>87.99852289512556</v>
+        <v>87.92466765140325</v>
       </c>
       <c r="D22" t="n">
-        <v>69.93563044301401</v>
+        <v>69.7841726618705</v>
       </c>
       <c r="E22" t="n">
-        <v>33.5939225858076</v>
+        <v>0.009144608837579641</v>
       </c>
       <c r="F22" t="n">
-        <v>3.489152818866943</v>
+        <v>0.003153040883178681</v>
       </c>
       <c r="G22" t="n">
         <v>27.33008493898488</v>
@@ -1151,7 +1153,7 @@
         <v>3.838074287247806</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.1580234574685475</v>
       </c>
     </row>
     <row r="23">
@@ -1166,16 +1168,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>86.22599704579025</v>
+        <v>88.25701624815362</v>
       </c>
       <c r="D23" t="n">
         <v>71.41234380916319</v>
       </c>
       <c r="E23" t="n">
-        <v>1.398256391325233</v>
+        <v>1.398256391325244</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8544053450143172</v>
+        <v>0.8544053450143316</v>
       </c>
       <c r="G23" t="n">
         <v>27.33008493898488</v>
@@ -1184,7 +1186,7 @@
         <v>3.838074287247806</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6606936172752509</v>
+        <v>0.6606936172752502</v>
       </c>
     </row>
     <row r="24">
@@ -1205,10 +1207,10 @@
         <v>67.55017039000379</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07918362115626934</v>
+        <v>0.07918362115626915</v>
       </c>
       <c r="F24" t="n">
-        <v>0.009217981857391588</v>
+        <v>0.009217981857391524</v>
       </c>
       <c r="G24" t="n">
         <v>27.33008493898488</v>
@@ -1232,13 +1234,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>95.56868537666175</v>
+        <v>92.17134416543574</v>
       </c>
       <c r="D25" t="n">
-        <v>64.7860658841348</v>
+        <v>64.63460810299129</v>
       </c>
       <c r="E25" t="n">
-        <v>0.009832116151674855</v>
+        <v>0.009832116151674867</v>
       </c>
       <c r="F25" t="n">
         <v>0.002877974130467129</v>
@@ -1250,7 +1252,7 @@
         <v>3.838074287247806</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2627717815316532</v>
+        <v>-0.2627717815316539</v>
       </c>
     </row>
     <row r="26">
@@ -1271,10 +1273,10 @@
         <v>70.62621045836023</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0008422651574759397</v>
+        <v>2.801373913764975</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0002324576316967389</v>
+        <v>0.7731540830233534</v>
       </c>
       <c r="G26" t="n">
         <v>11.43006373968069</v>
@@ -1283,7 +1285,7 @@
         <v>2.547216627733361</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2811735083958489</v>
+        <v>0.4958945150499567</v>
       </c>
     </row>
     <row r="27">
@@ -1298,16 +1300,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>92.16224458676426</v>
+        <v>81.48825861543153</v>
       </c>
       <c r="D27" t="n">
-        <v>71.75597159457715</v>
+        <v>69.6901226597805</v>
       </c>
       <c r="E27" t="n">
-        <v>0.005347822391421648</v>
+        <v>0.005347565429358135</v>
       </c>
       <c r="F27" t="n">
-        <v>0.002782924332814382</v>
+        <v>0.002776990775993524</v>
       </c>
       <c r="G27" t="n">
         <v>11.43006373968069</v>
@@ -1316,7 +1318,7 @@
         <v>2.547216627733361</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.130887858309768</v>
+        <v>-0.1309454503210832</v>
       </c>
     </row>
     <row r="28">
@@ -1331,16 +1333,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>84.53796889295516</v>
+        <v>84.50747179017993</v>
       </c>
       <c r="D28" t="n">
-        <v>71.56229825693997</v>
+        <v>70.9812782440284</v>
       </c>
       <c r="E28" t="n">
-        <v>13.62265806528406</v>
+        <v>0.005515376361654982</v>
       </c>
       <c r="F28" t="n">
-        <v>2.024824771742138</v>
+        <v>0.003056005953373127</v>
       </c>
       <c r="G28" t="n">
         <v>11.43006373968069</v>
@@ -1349,7 +1351,7 @@
         <v>2.547216627733361</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>-0.09328340204168503</v>
       </c>
     </row>
     <row r="29">
@@ -1364,16 +1366,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>81.79322964318389</v>
+        <v>81.82372674595914</v>
       </c>
       <c r="D29" t="n">
-        <v>70.17430600387347</v>
+        <v>70.81988379599741</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4998665328260713</v>
+        <v>0.4998665328260746</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7743241813435499</v>
+        <v>0.7743241813436287</v>
       </c>
       <c r="G29" t="n">
         <v>11.43006373968069</v>
@@ -1382,7 +1384,7 @@
         <v>2.547216627733361</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4820146434462483</v>
+        <v>0.4820146434462487</v>
       </c>
     </row>
     <row r="30">
@@ -1397,16 +1399,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>80.90881366270204</v>
+        <v>80.93931076547727</v>
       </c>
       <c r="D30" t="n">
         <v>68.78631375080697</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02873725541175773</v>
+        <v>0.02873725541175771</v>
       </c>
       <c r="F30" t="n">
-        <v>0.007834447931081059</v>
+        <v>0.007834447931081099</v>
       </c>
       <c r="G30" t="n">
         <v>11.43006373968069</v>
@@ -1415,7 +1417,7 @@
         <v>2.547216627733361</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3803302385319818</v>
+        <v>0.3803302385319811</v>
       </c>
     </row>
     <row r="31">
@@ -1430,16 +1432,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>97.34675205855444</v>
+        <v>81.30527599878012</v>
       </c>
       <c r="D31" t="n">
-        <v>31.08457069076824</v>
+        <v>69.6901226597805</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004225068855159842</v>
+        <v>0.004225068855159837</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.002505163385184185</v>
+        <v>0.002505163385184184</v>
       </c>
       <c r="G31" t="n">
         <v>11.43006373968069</v>
@@ -1448,7 +1450,7 @@
         <v>2.547216627733361</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1395949682121579</v>
+        <v>-0.1395949682121581</v>
       </c>
     </row>
   </sheetData>
